--- a/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/22. IC卡小计.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/22. IC卡小计.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="140">
   <si>
     <t>业务属性</t>
   </si>
@@ -254,9 +254,6 @@
   </si>
   <si>
     <t>数值</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>0</t>
@@ -449,14 +446,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1022,48 +1012,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1073,117 +1066,120 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1197,10 +1193,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1209,7 +1202,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1222,12 +1218,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1868,52 +1858,52 @@
       <c r="Q4" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="6">
+        <v>22</v>
+      </c>
+      <c r="S4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="X4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" ht="72" spans="1:30">
       <c r="A5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>69</v>
@@ -1928,14 +1918,14 @@
         <v>72</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>75</v>
@@ -1953,52 +1943,52 @@
       <c r="Q5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="6">
+        <v>22</v>
+      </c>
+      <c r="S5" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="U5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="V5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y5" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z5" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AA5" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="AB5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC5" s="6" t="s">
+      <c r="AD5" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:30">
       <c r="A6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>69</v>
@@ -2013,10 +2003,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -2037,54 +2027,54 @@
         <v>79</v>
       </c>
       <c r="R6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="T6" t="s">
         <v>106</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z6" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="U6" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="X6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y6" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z6" s="6" t="s">
+      <c r="AA6" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="AA6" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="AB6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC6" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC6" s="6" t="s">
+      <c r="AD6" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD6" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="7" ht="72" spans="1:30">
       <c r="A7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>69</v>
@@ -2099,14 +2089,14 @@
         <v>72</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>75</v>
@@ -2124,52 +2114,52 @@
       <c r="Q7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="R7" s="6">
+        <v>22</v>
+      </c>
+      <c r="S7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="U7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="V7" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V7" s="6" t="s">
+      <c r="W7" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="Y7" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y7" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z7" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AB7" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC7" s="6" t="s">
+      <c r="AD7" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD7" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="8" ht="72" spans="1:30">
       <c r="A8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>69</v>
@@ -2184,10 +2174,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
@@ -2196,7 +2186,7 @@
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>77</v>
@@ -2207,52 +2197,52 @@
       <c r="Q8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="6" t="s">
+      <c r="R8" s="6">
+        <v>22</v>
+      </c>
+      <c r="S8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="U8" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="V8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V8" s="6" t="s">
+      <c r="W8" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="Y8" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y8" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z8" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC8" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC8" s="6" t="s">
+      <c r="AD8" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD8" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="9" ht="72" spans="1:30">
       <c r="A9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>69</v>
@@ -2267,10 +2257,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -2285,53 +2275,55 @@
         <v>77</v>
       </c>
       <c r="P9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q9" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="Q9" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="R9" s="6"/>
+      <c r="R9" s="6">
+        <v>7</v>
+      </c>
       <c r="S9" s="6"/>
       <c r="U9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V9" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="W9" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="Y9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y9" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA9" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="AA9" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="AB9" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC9" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC9" s="6" t="s">
+      <c r="AD9" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD9" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" ht="72" spans="1:30">
       <c r="A10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>69</v>
@@ -2346,10 +2338,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -2358,7 +2350,7 @@
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>77</v>
@@ -2369,52 +2361,52 @@
       <c r="Q10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R10" s="6" t="s">
+      <c r="R10" s="6">
+        <v>22</v>
+      </c>
+      <c r="S10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="U10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U10" s="6" t="s">
+      <c r="V10" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V10" s="6" t="s">
+      <c r="W10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W10" s="6" t="s">
+      <c r="X10" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="Y10" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y10" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z10" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AB10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC10" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC10" s="6" t="s">
+      <c r="AD10" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD10" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:30">
       <c r="A11" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>69</v>
@@ -2429,10 +2421,10 @@
         <v>72</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
@@ -2447,42 +2439,44 @@
         <v>77</v>
       </c>
       <c r="P11" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q11" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="Q11" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="R11" s="6"/>
+      <c r="R11" s="6">
+        <v>7</v>
+      </c>
       <c r="S11" s="6"/>
       <c r="U11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V11" s="6" t="s">
+      <c r="W11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W11" s="6" t="s">
+      <c r="X11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X11" s="6" t="s">
+      <c r="Y11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y11" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA11" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="AA11" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="AB11" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC11" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC11" s="6" t="s">
+      <c r="AD11" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD11" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
